--- a/files/cleaning-log.xlsx
+++ b/files/cleaning-log.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Column quality, אחרי entire data set: Error 1</t>
+          <t>אחרי המרה ל־Date, Column quality ב־entire data set: Error 1</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">

--- a/files/cleaning-log.xlsx
+++ b/files/cleaning-log.xlsx
@@ -498,7 +498,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>שיעור 3: ממלאות בדיעבד, מתוך Applied Steps, את התיקונים של שיעורים 2 ו־3. מכאן — שורה אחת לכל תיקון, בסוף כל חדר.</t>
+          <t>שיעור 3: ממלאות יחד, מתוך Applied Steps, את התיקונים בתדלוק. בחדר, על ההזמנות: קודם רושמות את הבעיות (עמודה, הבעיה, איך גיליתי), ואחרי התיקון משלימות את השאר.</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,11 @@
       <c r="D5" s="5" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="5" t="n"/>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>הזמנות בלי חודש ((Blank) בגרף)</t>
+        </is>
+      </c>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="n"/>

--- a/files/cleaning-log.xlsx
+++ b/files/cleaning-log.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תיעוד הטיוב" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="לפני ואחרי" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מסד ראשי" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="קובץ משלים" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,22 +28,21 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="16"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <i val="1"/>
-      <color rgb="00555555"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00444444"/>
+      <color rgb="00808080"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -52,12 +51,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F6F5C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EEF3F1"/>
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,34 +65,43 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B8C2BE"/>
+        <color rgb="00999999"/>
       </left>
       <right style="thin">
-        <color rgb="00B8C2BE"/>
+        <color rgb="00999999"/>
       </right>
       <top style="thin">
-        <color rgb="00B8C2BE"/>
+        <color rgb="00999999"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B8C2BE"/>
+        <color rgb="00999999"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,268 +468,488 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>טבלת תיעוד הטיוב</t>
+          <t>טבלת הטיוב — פרק 3 בעבודה הכתובה</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">שמות: </t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">המסד / הקובץ: </t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>שמות:</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>הקובץ:</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>שיעור 3: ממלאות יחד, מתוך Applied Steps, את התיקונים בתדלוק. בחדר, על ההזמנות: קודם רושמות את הבעיות (עמודה, הבעיה, איך גיליתי), ואחרי התיקון משלימות את השאר.</t>
+          <t>גיליון לכל קובץ במסד. כותבות גם 0 — אבל רק אחרי שבחלק א כתוב איך בדקתן. הסבר ודוגמה מלאה: https://enavcorem.github.io/powerbi-lessons/tiyuv.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>עמודה</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+          <t>חלק א: איך בדקנו (פעם אחת לכל הקובץ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>הבעיה</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>איך גיליתי</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>מה עשיתי</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>למה (ולמה לא הדרך האחרת)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>שם השלב ביומן</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>תאריך (דוגמה — תדלוק)</t>
-        </is>
-      </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>שגיאה בשורה אחת</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>אחרי המרה ל־Date, Column quality ב־entire data set: Error 1</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Replace Errors ← 01/01/2026</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>הערך היה טקסט ולא תאריך. כל שאר השורה תקין, ולכן החלפתי ולא מחקתי</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>תיקון תאריך שגוי</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="n"/>
+          <t>איך בדקנו: הכלי, ומה בדיוק הסתכלנו</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>חסרים</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>למשל: Empty בפרופיל, ואז סינון על null</t>
+        </is>
+      </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>שגויים</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>למשל: שינוי לסוג הנכון, ואז Error בפרופיל</t>
+        </is>
+      </c>
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>חריגים</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>למשל: Min ו־Max, או Box Plot באקסל</t>
+        </is>
+      </c>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>כפולים</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>למשל: Keep Duplicates על המפתח, או COUNTIF</t>
+        </is>
+      </c>
       <c r="C10" s="5" t="n"/>
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>המפתח</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>מה מזהה רשומה, ולמה בחרנו בו</t>
+        </is>
+      </c>
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="32" customHeight="1">
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>חלק ב: שורה לכל עמודה שמשמשת את הניתוח</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>עמודה</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>תקינות</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>חריגים</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>חסרים</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>כפולים (רק במפתח, אחרת —)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>שגויים</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>אחוז שגויים</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>מה עשינו ולמה (ולמה לא הדרך האחרת) · שם השלב ביומן או איפה באקסל</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="5" t="n"/>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="32" customHeight="1">
+      <c r="G15" s="8">
+        <f>IF(COUNT(B15:F15)=0,"",SUM(C15:F15)/SUM(B15:F15))</f>
+        <v/>
+      </c>
+      <c r="H15" s="5" t="n"/>
+    </row>
+    <row r="16">
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="32" customHeight="1">
+      <c r="G16" s="8">
+        <f>IF(COUNT(B16:F16)=0,"",SUM(C16:F16)/SUM(B16:F16))</f>
+        <v/>
+      </c>
+      <c r="H16" s="5" t="n"/>
+    </row>
+    <row r="17">
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="32" customHeight="1">
+      <c r="G17" s="8">
+        <f>IF(COUNT(B17:F17)=0,"",SUM(C17:F17)/SUM(B17:F17))</f>
+        <v/>
+      </c>
+      <c r="H17" s="5" t="n"/>
+    </row>
+    <row r="18">
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="32" customHeight="1">
+      <c r="G18" s="8">
+        <f>IF(COUNT(B18:F18)=0,"",SUM(C18:F18)/SUM(B18:F18))</f>
+        <v/>
+      </c>
+      <c r="H18" s="5" t="n"/>
+    </row>
+    <row r="19">
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="32" customHeight="1">
+      <c r="G19" s="8">
+        <f>IF(COUNT(B19:F19)=0,"",SUM(C19:F19)/SUM(B19:F19))</f>
+        <v/>
+      </c>
+      <c r="H19" s="5" t="n"/>
+    </row>
+    <row r="20">
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="5" t="n"/>
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="32" customHeight="1">
+      <c r="G20" s="8">
+        <f>IF(COUNT(B20:F20)=0,"",SUM(C20:F20)/SUM(B20:F20))</f>
+        <v/>
+      </c>
+      <c r="H20" s="5" t="n"/>
+    </row>
+    <row r="21">
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="5" t="n"/>
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="32" customHeight="1">
+      <c r="G21" s="8">
+        <f>IF(COUNT(B21:F21)=0,"",SUM(C21:F21)/SUM(B21:F21))</f>
+        <v/>
+      </c>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22">
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="5" t="n"/>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="32" customHeight="1">
+      <c r="G22" s="8">
+        <f>IF(COUNT(B22:F22)=0,"",SUM(C22:F22)/SUM(B22:F22))</f>
+        <v/>
+      </c>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23">
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="5" t="n"/>
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="32" customHeight="1">
+      <c r="G23" s="8">
+        <f>IF(COUNT(B23:F23)=0,"",SUM(C23:F23)/SUM(B23:F23))</f>
+        <v/>
+      </c>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24">
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="5" t="n"/>
       <c r="D24" s="5" t="n"/>
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="32" customHeight="1">
+      <c r="G24" s="8">
+        <f>IF(COUNT(B24:F24)=0,"",SUM(C24:F24)/SUM(B24:F24))</f>
+        <v/>
+      </c>
+      <c r="H24" s="5" t="n"/>
+    </row>
+    <row r="25">
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="5" t="n"/>
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="32" customHeight="1">
+      <c r="G25" s="8">
+        <f>IF(COUNT(B25:F25)=0,"",SUM(C25:F25)/SUM(B25:F25))</f>
+        <v/>
+      </c>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26">
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="5" t="n"/>
       <c r="D26" s="5" t="n"/>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
+      <c r="G26" s="8">
+        <f>IF(COUNT(B26:F26)=0,"",SUM(C26:F26)/SUM(B26:F26))</f>
+        <v/>
+      </c>
+      <c r="H26" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>חלק ג: מה ירד, וכמה נשאר</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>עמודות שהורדנו</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>אילו, ולמה</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>שורות ריקות לגמרי</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>כמה, ומה עשינו</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr"/>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>לפני</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>אחרי</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>מה השתנה, ולמה</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>מספר שורות</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>רשות: מספר מהדוח —</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>רשות: מספר מהדוח —</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="D31:H31"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -737,81 +960,488 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>המספרים בדוח, לפני הטיוב ואחריו</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>מה מודדים</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>לפני</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>אחרי</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>מה השתנה, ולמה</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>סך הכל מכירות (Sum)</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>מספר הזמנות (Count)</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>הזמנות בלי חודש ((Blank) בגרף)</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
+          <t>טבלת הטיוב — פרק 3 בעבודה הכתובה</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>שמות:</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>הקובץ:</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>גיליון לכל קובץ במסד. כותבות גם 0 — אבל רק אחרי שבחלק א כתוב איך בדקתן. הסבר ודוגמה מלאה: https://enavcorem.github.io/powerbi-lessons/tiyuv.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>חלק א: איך בדקנו (פעם אחת לכל הקובץ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>הבעיה</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>איך בדקנו: הכלי, ומה בדיוק הסתכלנו</t>
+        </is>
+      </c>
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>חסרים</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>למשל: Empty בפרופיל, ואז סינון על null</t>
+        </is>
+      </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>שגויים</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>למשל: שינוי לסוג הנכון, ואז Error בפרופיל</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>חריגים</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>למשל: Min ו־Max, או Box Plot באקסל</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>כפולים</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>למשל: Keep Duplicates על המפתח, או COUNTIF</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>המפתח</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>מה מזהה רשומה, ולמה בחרנו בו</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>חלק ב: שורה לכל עמודה שמשמשת את הניתוח</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>עמודה</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>תקינות</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>חריגים</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>חסרים</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>כפולים (רק במפתח, אחרת —)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>שגויים</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>אחוז שגויים</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>מה עשינו ולמה (ולמה לא הדרך האחרת) · שם השלב ביומן או איפה באקסל</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="8">
+        <f>IF(COUNT(B15:F15)=0,"",SUM(C15:F15)/SUM(B15:F15))</f>
+        <v/>
+      </c>
+      <c r="H15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="8">
+        <f>IF(COUNT(B16:F16)=0,"",SUM(C16:F16)/SUM(B16:F16))</f>
+        <v/>
+      </c>
+      <c r="H16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="8">
+        <f>IF(COUNT(B17:F17)=0,"",SUM(C17:F17)/SUM(B17:F17))</f>
+        <v/>
+      </c>
+      <c r="H17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="8">
+        <f>IF(COUNT(B18:F18)=0,"",SUM(C18:F18)/SUM(B18:F18))</f>
+        <v/>
+      </c>
+      <c r="H18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="8">
+        <f>IF(COUNT(B19:F19)=0,"",SUM(C19:F19)/SUM(B19:F19))</f>
+        <v/>
+      </c>
+      <c r="H19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="8">
+        <f>IF(COUNT(B20:F20)=0,"",SUM(C20:F20)/SUM(B20:F20))</f>
+        <v/>
+      </c>
+      <c r="H20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="8">
+        <f>IF(COUNT(B21:F21)=0,"",SUM(C21:F21)/SUM(B21:F21))</f>
+        <v/>
+      </c>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="8">
+        <f>IF(COUNT(B22:F22)=0,"",SUM(C22:F22)/SUM(B22:F22))</f>
+        <v/>
+      </c>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="8">
+        <f>IF(COUNT(B23:F23)=0,"",SUM(C23:F23)/SUM(B23:F23))</f>
+        <v/>
+      </c>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="8">
+        <f>IF(COUNT(B24:F24)=0,"",SUM(C24:F24)/SUM(B24:F24))</f>
+        <v/>
+      </c>
+      <c r="H24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="8">
+        <f>IF(COUNT(B25:F25)=0,"",SUM(C25:F25)/SUM(B25:F25))</f>
+        <v/>
+      </c>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="8">
+        <f>IF(COUNT(B26:F26)=0,"",SUM(C26:F26)/SUM(B26:F26))</f>
+        <v/>
+      </c>
+      <c r="H26" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>חלק ג: מה ירד, וכמה נשאר</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>עמודות שהורדנו</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>אילו, ולמה</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>שורות ריקות לגמרי</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>כמה, ומה עשינו</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr"/>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>לפני</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>אחרי</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>מה השתנה, ולמה</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>מספר שורות</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>רשות: מספר מהדוח —</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>רשות: מספר מהדוח —</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="D31:H31"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>